--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486315_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486315_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8092</v>
+        <v>4.2544</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7464</v>
+        <v>4.8834</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9372</v>
+        <v>-0.6289</v>
       </c>
       <c r="G2" t="n">
         <v>3.6122</v>
@@ -610,13 +610,13 @@
         <v>1.0875</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0635</v>
+        <v>-0.6183</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6813</v>
+        <v>-0.5444</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3822</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>0.3904</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2537</v>
+        <v>2.6737</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0244</v>
+        <v>5.1361</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.7706</v>
+        <v>-2.4624</v>
       </c>
       <c r="G3" t="n">
         <v>2.2982</v>
@@ -688,13 +688,13 @@
         <v>1.0875</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9145</v>
+        <v>-0.4945</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6249</v>
+        <v>-0.5131</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2896</v>
+        <v>0.0186</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7947</v>
+        <v>1.1995</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9879</v>
+        <v>0.4543</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8068</v>
+        <v>0.7452</v>
       </c>
       <c r="G4" t="n">
         <v>1.0363</v>
@@ -766,13 +766,13 @@
         <v>0.6525</v>
       </c>
       <c r="S4" t="n">
-        <v>1.151</v>
+        <v>0.5558</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7607</v>
+        <v>0.2271</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3903</v>
+        <v>0.3287</v>
       </c>
       <c r="V4" t="n">
         <v>1.13</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. MC GREW</t>
+          <t>M. SOLA IDRISU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8852</v>
+        <v>0.1501</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2517</v>
+        <v>-0.0502</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6334</v>
+        <v>0.2004</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2276</v>
+        <v>0.3163</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8696</v>
+        <v>0.3163</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0973</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7639</v>
+        <v>0.0182</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8244</v>
+        <v>0.0182</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9395</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9916</v>
+        <v>0.298</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0452</v>
+        <v>0.298</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.0368</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.5225</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3926</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.0704</v>
+        <v>-0.1661</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1202</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>1.9502</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. SOLA IDRISU</t>
+          <t>T. MC GREW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1193</v>
+        <v>-0.5174</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0502</v>
+        <v>-0.1953</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1696</v>
+        <v>-0.3221</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3163</v>
+        <v>-0.2276</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3163</v>
+        <v>0.8696</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-1.0973</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0182</v>
+        <v>1.7639</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0182</v>
+        <v>0.8244</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.9395</v>
       </c>
       <c r="M6" t="n">
-        <v>0.298</v>
+        <v>-1.9916</v>
       </c>
       <c r="N6" t="n">
-        <v>0.298</v>
+        <v>0.0452</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-2.0368</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.3926</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.197</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.3268</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1285</v>
+        <v>0.9947</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. NWOGBO</t>
+          <t>L. GIOVANNETTI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0789</v>
+        <v>-0.9984</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4412</v>
+        <v>-0.1683</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5201</v>
+        <v>-0.8300999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6085</v>
+        <v>0.2586</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3526</v>
+        <v>0.1701</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.2559</v>
+        <v>0.0885</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9988</v>
+        <v>-0.1166</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.2283</v>
+        <v>0.073</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2295</v>
+        <v>-0.1896</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6097</v>
+        <v>0.3752</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8757</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4854</v>
+        <v>0.2781</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5089</v>
+        <v>0.2205</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4867</v>
+        <v>-0.0517</v>
       </c>
       <c r="U7" t="n">
-        <v>2.0222</v>
+        <v>0.2722</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5443</v>
+        <v>-1.695</v>
       </c>
       <c r="W7" t="n">
-        <v>3.0408</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.5851</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. GIOVANNETTI</t>
+          <t>A. BRIMAH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9021</v>
+        <v>-1.5064</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6405999999999999</v>
+        <v>-1.3333</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2616</v>
+        <v>-0.1731</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2586</v>
+        <v>-0.7655</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1701</v>
+        <v>-1.1042</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0885</v>
+        <v>0.3386</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1166</v>
+        <v>0.1232</v>
       </c>
       <c r="K8" t="n">
-        <v>0.073</v>
+        <v>-0.1063</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1896</v>
+        <v>0.2295</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3752</v>
+        <v>-0.8887</v>
       </c>
       <c r="N8" t="n">
-        <v>0.09710000000000001</v>
+        <v>-0.9978</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2781</v>
+        <v>0.1091</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2175</v>
+        <v>-0.87</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6833</v>
+        <v>-0.2406</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5239</v>
+        <v>-0.1514</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1593</v>
+        <v>-0.0892</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.695</v>
+        <v>0.3698</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.695</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. BRIMAH</t>
+          <t>L. NWOGBO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3311</v>
+        <v>-1.8223</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0038</v>
+        <v>0.6842</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3273</v>
+        <v>-2.5065</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7655</v>
+        <v>-1.6085</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1042</v>
+        <v>-0.3526</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3386</v>
+        <v>-1.2559</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1232</v>
+        <v>-0.9988</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1063</v>
+        <v>-1.2283</v>
       </c>
       <c r="L9" t="n">
         <v>0.2295</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8887</v>
+        <v>-0.6097</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9978</v>
+        <v>0.8757</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1091</v>
+        <v>-1.4854</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.87</v>
+        <v>-0.435</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="R9" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0653</v>
+        <v>0.7655</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.822</v>
+        <v>-0.2704</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2434</v>
+        <v>1.0358</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3698</v>
+        <v>-0.5443</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.0408</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3698</v>
+        <v>-3.5851</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1719</v>
+        <v>-2.2797</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.352</v>
+        <v>-1.768</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8199</v>
+        <v>-0.5117</v>
       </c>
       <c r="G10" t="n">
         <v>-1.9975</v>
@@ -1234,13 +1234,13 @@
         <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9145</v>
+        <v>-0.0222</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2089</v>
+        <v>-0.6249</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2944</v>
+        <v>0.6026</v>
       </c>
       <c r="V10" t="n">
         <v>-1.13</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7627</v>
+        <v>-3.1616</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3814</v>
+        <v>-2.9344</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3813</v>
+        <v>-0.2272</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3582</v>
@@ -1312,13 +1312,13 @@
         <v>0.2175</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2518</v>
+        <v>0.3494</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.536</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2842</v>
+        <v>0.4383</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1952</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.9873</v>
+        <v>-6.6791</v>
       </c>
       <c r="E12" t="n">
         <v>-5.4888</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4985</v>
+        <v>-1.1903</v>
       </c>
       <c r="G12" t="n">
         <v>-3.3017</v>
@@ -1390,13 +1390,13 @@
         <v>0.435</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6405</v>
+        <v>-0.3323</v>
       </c>
       <c r="T12" t="n">
         <v>-0.008399999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6321</v>
+        <v>-0.3239</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,37 +1423,37 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.371900000000002</v>
+        <v>-8.687199999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.465199999999999</v>
+        <v>-0.7803000000000004</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.906699999999999</v>
+        <v>-7.9067</v>
       </c>
       <c r="G13" t="n">
         <v>-1.7374</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8204000000000002</v>
+        <v>0.8204000000000007</v>
       </c>
       <c r="I13" t="n">
         <v>-2.5578</v>
       </c>
       <c r="J13" t="n">
-        <v>7.0894</v>
+        <v>7.089399999999999</v>
       </c>
       <c r="K13" t="n">
         <v>0.8536000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>6.235799999999998</v>
+        <v>6.235799999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.827000000000002</v>
+        <v>-8.827</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.03330000000000005</v>
+        <v>-0.03329999999999994</v>
       </c>
       <c r="O13" t="n">
         <v>-8.793700000000001</v>
@@ -1468,13 +1468,13 @@
         <v>6.524999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.99999999995449e-05</v>
+        <v>0.6849999999999996</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.1063</v>
+        <v>-2.421400000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>3.1062</v>
+        <v>3.1063</v>
       </c>
       <c r="V13" t="n">
         <v>-1.1093</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.4343</v>
+        <v>5.329</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9629</v>
+        <v>2.7394</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4714</v>
+        <v>2.5896</v>
       </c>
       <c r="G14" t="n">
         <v>1.4209</v>
@@ -1546,13 +1546,13 @@
         <v>1.7401</v>
       </c>
       <c r="S14" t="n">
-        <v>0.197</v>
+        <v>0.0916</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2019</v>
+        <v>-0.4254</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3988</v>
+        <v>0.517</v>
       </c>
       <c r="V14" t="n">
         <v>3.1639</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.9657</v>
+        <v>4.4712</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5147</v>
+        <v>3.1794</v>
       </c>
       <c r="F15" t="n">
-        <v>1.451</v>
+        <v>1.2918</v>
       </c>
       <c r="G15" t="n">
         <v>3.4239</v>
@@ -1624,13 +1624,13 @@
         <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>1.132</v>
+        <v>0.6375</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3257</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8063</v>
+        <v>0.6471</v>
       </c>
       <c r="V15" t="n">
         <v>-0.4603</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.386</v>
+        <v>4.2249</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3952</v>
+        <v>3.1775</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9909</v>
+        <v>1.0474</v>
       </c>
       <c r="G16" t="n">
         <v>3.5623</v>
@@ -1702,13 +1702,13 @@
         <v>1.5225</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9113</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3699</v>
+        <v>-0.5876</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4587</v>
+        <v>0.5152</v>
       </c>
       <c r="V16" t="n">
         <v>0.2999</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.0775</v>
+        <v>3.2329</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7004</v>
+        <v>0.5886</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3771</v>
+        <v>2.6443</v>
       </c>
       <c r="G17" t="n">
         <v>0.459</v>
@@ -1780,13 +1780,13 @@
         <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1405</v>
+        <v>0.2959</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2584</v>
+        <v>-0.3701</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3988</v>
+        <v>0.666</v>
       </c>
       <c r="V17" t="n">
         <v>0.9554</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4111</v>
+        <v>1.8287</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5507</v>
+        <v>2.886</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1396</v>
+        <v>-1.0573</v>
       </c>
       <c r="G18" t="n">
         <v>1.3475</v>
@@ -1858,13 +1858,13 @@
         <v>1.9576</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7639</v>
+        <v>-0.3464</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9349</v>
+        <v>-0.5996</v>
       </c>
       <c r="U18" t="n">
-        <v>0.171</v>
+        <v>0.2532</v>
       </c>
       <c r="V18" t="n">
         <v>-1.13</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8979</v>
+        <v>1.0507</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3424</v>
+        <v>0.0071</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5555</v>
+        <v>1.0436</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9945000000000001</v>
@@ -1936,13 +1936,13 @@
         <v>1.7401</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2174</v>
+        <v>-0.0646</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0156</v>
+        <v>-0.3196</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.233</v>
+        <v>0.2551</v>
       </c>
       <c r="V19" t="n">
         <v>0.3698</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. DE SOUZA PACHECO</t>
+          <t>C. VARELA ROMERO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1828</v>
+        <v>0.149</v>
       </c>
       <c r="E20" t="n">
-        <v>2.3864</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2036</v>
+        <v>0.149</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6808</v>
+        <v>0.149</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0946</v>
+        <v>0.149</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7753</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4909</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7609</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1716</v>
+        <v>0.149</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6663</v>
+        <v>0.149</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.5053</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9557</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4627</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.493</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1254</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.5204</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.395</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. VARELA ROMERO</t>
+          <t>C. DE SOUZA PACHECO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.149</v>
+        <v>-0.2835</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1.8276</v>
       </c>
       <c r="F21" t="n">
-        <v>0.149</v>
+        <v>-2.1111</v>
       </c>
       <c r="G21" t="n">
-        <v>0.149</v>
+        <v>-0.6808</v>
       </c>
       <c r="H21" t="n">
-        <v>0.149</v>
+        <v>0.0946</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-0.7753</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1.4909</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.7609</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="M21" t="n">
-        <v>0.149</v>
+        <v>-2.1716</v>
       </c>
       <c r="N21" t="n">
-        <v>0.149</v>
+        <v>-0.6663</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-1.5053</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>0.4894</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>-0.0961</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>0.5855</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.1254</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.5204</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.395</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. BRNOVIC</t>
+          <t>J. CREMO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5919</v>
+        <v>-1.4277</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.001</v>
+        <v>-2.7623</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5909</v>
+        <v>1.3346</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1535</v>
+        <v>-1.4115</v>
       </c>
       <c r="H22" t="n">
-        <v>0.292</v>
+        <v>-1.77</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.4455</v>
+        <v>0.3586</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4531</v>
+        <v>-1.0144</v>
       </c>
       <c r="K22" t="n">
-        <v>0.292</v>
+        <v>-1.6663</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7451</v>
+        <v>0.6519</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7004</v>
+        <v>-0.397</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>-0.1038</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7004</v>
+        <v>-0.2933</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2175</v>
+        <v>1.7401</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4317</v>
+        <v>-0.2085</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5396</v>
+        <v>-0.8556</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1079</v>
+        <v>0.6471</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.4603</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.6555</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. THIAM</t>
+          <t>D. BRNOVIC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5494</v>
+        <v>-1.7538</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6733</v>
+        <v>-1.2245</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8762</v>
+        <v>-0.5292</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.659</v>
+        <v>-1.1535</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.1864</v>
+        <v>0.292</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4726</v>
+        <v>-1.4455</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.6508</v>
+        <v>-0.4531</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.9186</v>
+        <v>0.292</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2677</v>
+        <v>-0.7451</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0082</v>
+        <v>-0.7004</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2679</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7403</v>
+        <v>-0.7004</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2175</v>
+        <v>-0.87</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R23" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7175</v>
+        <v>0.2698</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0649</v>
+        <v>0.316</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7824</v>
+        <v>-0.0463</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.5204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. CREMO</t>
+          <t>A. THIAM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.567</v>
+        <v>-2.8268</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.3211</v>
+        <v>-1.6733</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7541</v>
+        <v>-1.1536</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.4115</v>
+        <v>-2.659</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.77</v>
+        <v>-2.1864</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3586</v>
+        <v>-0.4726</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.0144</v>
+        <v>-1.6508</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.6663</v>
+        <v>-1.9186</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6519</v>
+        <v>0.2677</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.397</v>
+        <v>-1.0082</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1038</v>
+        <v>-0.2679</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2933</v>
+        <v>-0.7403</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6525</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q24" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R24" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3478</v>
+        <v>0.4401</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.4144</v>
+        <v>-0.0649</v>
       </c>
       <c r="U24" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.505</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.4603</v>
+        <v>-0.3904</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.6555</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.4242</v>
+        <v>-3.1326</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.9505</v>
+        <v>-0.8388</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.4737</v>
+        <v>-2.2938</v>
       </c>
       <c r="G25" t="n">
         <v>-1.726</v>
@@ -2404,13 +2404,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.334</v>
+        <v>-0.0424</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2055</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1285</v>
+        <v>0.0514</v>
       </c>
       <c r="V25" t="n">
         <v>-1.3642</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>9.3718</v>
+        <v>10.862</v>
       </c>
       <c r="E26" t="n">
-        <v>7.906800000000002</v>
+        <v>7.906700000000002</v>
       </c>
       <c r="F26" t="n">
-        <v>1.465000000000001</v>
+        <v>2.9553</v>
       </c>
       <c r="G26" t="n">
         <v>1.737299999999999</v>
@@ -2458,10 +2458,10 @@
         <v>8.826600000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.03309999999999935</v>
+        <v>0.03309999999999957</v>
       </c>
       <c r="L26" t="n">
-        <v>8.7935</v>
+        <v>8.793499999999998</v>
       </c>
       <c r="M26" t="n">
         <v>-7.089399999999999</v>
@@ -2482,13 +2482,13 @@
         <v>13.0504</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.665334536937735e-16</v>
+        <v>1.49</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.1063</v>
+        <v>-3.106200000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>3.1062</v>
+        <v>4.5963</v>
       </c>
       <c r="V26" t="n">
         <v>1.1092</v>
